--- a/data/processed/positivacao/2025-01_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2025-01_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26583,7 +26583,7 @@
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr"/>
@@ -37571,7 +37571,7 @@
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr"/>
@@ -65969,7 +65969,7 @@
     <row r="2526">
       <c r="A2526" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2526" t="inlineStr"/>
@@ -67588,12 +67588,12 @@
       <c r="A2589" t="inlineStr"/>
       <c r="B2589" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 3 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 8.342,57
+          <t>Vendedor 1 - VENDEDOR 01: positivou 3 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 8.342,57
 Vendedor 18 - LOJA: positivou 213 cliente(s), não positivou 696 cliente(s) - Total vendido: R$ 73.688,84
-Vendedor 3 - FERNANDA: positivou 106 cliente(s), não positivou 316 cliente(s) - Total vendido: R$ 172.574,08
-Vendedor 4 - DANIELA: positivou 115 cliente(s), não positivou 532 cliente(s) - Total vendido: R$ 58.179,07
+Vendedor 3 - VENDEDOR 03: positivou 106 cliente(s), não positivou 316 cliente(s) - Total vendido: R$ 172.574,08
+Vendedor 4 - VENDEDOR 04: positivou 115 cliente(s), não positivou 532 cliente(s) - Total vendido: R$ 58.179,07
 Vendedor 5 - SITE: positivou 2 cliente(s), não positivou 442 cliente(s) - Total vendido: R$ 534,45
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2589" t="inlineStr"/>
